--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF2B9D0-8206-4BB7-ABEF-F667FBBBF3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BAC5F6-36BD-4703-B5B4-701C76042B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Desc" sheetId="1" r:id="rId2"/>
-    <sheet name="!Sample" sheetId="3" r:id="rId3"/>
+    <sheet name="ElementStatusTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BAC5F6-36BD-4703-B5B4-701C76042B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEEC237-8889-4320-B03A-CAE26290B798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -1213,6 +1213,33 @@
         </r>
       </text>
     </comment>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{59FC3F4E-9DAA-41C7-ACDC-25532DA66A65}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">1: 물리
+2: 화염
+3: 방사능
+4: 중력
+5: 공허
+6: 신성
+7: (물리+물리)
+8: (화염+화염)
+9: (방사능+방사능)
+10: (중력+중력)
+11: (공허+공허)
+12: (신성+신성)
+13: 카오스
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E3" authorId="0" shapeId="0" xr:uid="{C2095F88-B0F9-4F1B-B152-8ADD4BD51B2D}">
       <text>
         <r>
@@ -1760,7 +1787,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2092,10 +2119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상태 이상 표시명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2121,6 +2144,66 @@
   </si>
   <si>
     <t>Table_Element_Status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Status_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_STUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_BURN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_CONTAMINATION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_SUPPRESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_STRANGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_SILENCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_WEAKNESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_OVERHEAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_RADIAITON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_BIND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_CORRODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_DOMINATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_CHAOS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태 이상 표시명 키값</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2243,7 +2326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2266,13 +2349,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2367,6 +2463,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5027,18 +5135,18 @@
   <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.625" style="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5061,7 +5169,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>81</v>
@@ -5069,7 +5177,7 @@
       <c r="G2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="22"/>
+      <c r="H2" s="32"/>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
@@ -5114,7 +5222,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>82</v>
@@ -5122,7 +5230,7 @@
       <c r="G3" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="29"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
       <c r="K3" s="29"/>
@@ -5155,7 +5263,7 @@
     </row>
     <row r="4" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>57</v>
@@ -5171,7 +5279,7 @@
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
+      <c r="H4" s="34"/>
       <c r="I4" s="26"/>
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
@@ -5205,7 +5313,7 @@
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
-        <v>40011000</v>
+        <v>40011001</v>
       </c>
       <c r="B5" s="25">
         <v>40</v>
@@ -5213,17 +5321,19 @@
       <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="25">
-        <v>1000</v>
-      </c>
-      <c r="E5" s="24"/>
+      <c r="D5" s="24">
+        <v>1001</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>94</v>
+      </c>
       <c r="F5" s="24">
         <v>1</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="25"/>
+        <v>86</v>
+      </c>
+      <c r="H5" s="35"/>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
@@ -5257,7 +5367,7 @@
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f>(B6*1000000) + (C6*10000) + D6</f>
-        <v>40011001</v>
+        <v>40011002</v>
       </c>
       <c r="B6" s="25">
         <v>40</v>
@@ -5265,17 +5375,19 @@
       <c r="C6" s="25">
         <v>1</v>
       </c>
-      <c r="D6" s="25">
-        <v>1001</v>
-      </c>
-      <c r="E6" s="24"/>
+      <c r="D6" s="24">
+        <v>1002</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>95</v>
+      </c>
       <c r="F6" s="24">
         <v>2</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="25"/>
+        <v>86</v>
+      </c>
+      <c r="H6" s="35"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
@@ -5309,232 +5421,265 @@
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" ref="A7:A17" si="0">(B7*1000000) + (C7*10000) + D7</f>
-        <v>40011002</v>
+        <v>40011003</v>
       </c>
       <c r="B7" s="25">
         <v>40</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>1</v>
       </c>
-      <c r="D7" s="31">
-        <v>1002</v>
-      </c>
-      <c r="F7" s="30">
+      <c r="D7" s="24">
+        <v>1003</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="24">
         <v>3</v>
       </c>
-      <c r="G7" s="30" t="s">
-        <v>88</v>
+      <c r="G7" s="24" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
-        <v>40011003</v>
+        <v>40011004</v>
       </c>
       <c r="B8" s="25">
         <v>40</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="31">
-        <v>1003</v>
-      </c>
-      <c r="F8" s="30">
+      <c r="D8" s="24">
+        <v>1004</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="24">
         <v>4</v>
       </c>
-      <c r="G8" s="30" t="s">
-        <v>89</v>
+      <c r="G8" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
-        <v>40011004</v>
+        <v>40011005</v>
       </c>
       <c r="B9" s="25">
         <v>40</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="31">
-        <v>1004</v>
-      </c>
-      <c r="F9" s="30">
+      <c r="D9" s="24">
+        <v>1005</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="24">
         <v>5</v>
       </c>
-      <c r="G9" s="30" t="s">
-        <v>87</v>
+      <c r="G9" s="24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
-        <v>40011005</v>
+        <v>40011006</v>
       </c>
       <c r="B10" s="25">
         <v>40</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="25">
         <v>1</v>
       </c>
-      <c r="D10" s="31">
-        <v>1005</v>
-      </c>
-      <c r="F10" s="30">
+      <c r="D10" s="24">
+        <v>1006</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="24">
         <v>6</v>
       </c>
-      <c r="G10" s="30" t="s">
-        <v>87</v>
+      <c r="G10" s="24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
-        <v>40022000</v>
+        <v>40022001</v>
       </c>
       <c r="B11" s="25">
         <v>40</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="25">
         <v>2</v>
       </c>
-      <c r="D11" s="31">
-        <v>2000</v>
-      </c>
-      <c r="F11" s="30">
+      <c r="D11" s="24">
+        <v>2001</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="30" t="s">
-        <v>90</v>
+      <c r="G11" s="24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <f t="shared" si="0"/>
-        <v>40022001</v>
+        <v>40022002</v>
       </c>
       <c r="B12" s="25">
         <v>40</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="25">
         <v>2</v>
       </c>
-      <c r="D12" s="31">
-        <v>2001</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="D12" s="24">
+        <v>2002</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="24">
         <v>7</v>
       </c>
-      <c r="G12" s="30" t="s">
-        <v>87</v>
+      <c r="G12" s="24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <f t="shared" si="0"/>
-        <v>40022002</v>
+        <v>40022003</v>
       </c>
       <c r="B13" s="25">
         <v>40</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>2</v>
       </c>
-      <c r="D13" s="31">
-        <v>2002</v>
-      </c>
-      <c r="F13" s="30">
+      <c r="D13" s="24">
+        <v>2003</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="24">
         <v>3</v>
       </c>
-      <c r="G13" s="30" t="s">
-        <v>88</v>
+      <c r="G13" s="24" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <f t="shared" si="0"/>
-        <v>40022003</v>
+        <v>40022004</v>
       </c>
       <c r="B14" s="25">
         <v>40</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="25">
         <v>2</v>
       </c>
-      <c r="D14" s="31">
-        <v>2003</v>
-      </c>
-      <c r="F14" s="30">
+      <c r="D14" s="24">
+        <v>2004</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="24">
         <v>4</v>
       </c>
-      <c r="G14" s="30" t="s">
-        <v>89</v>
+      <c r="G14" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <f t="shared" si="0"/>
-        <v>40022004</v>
+        <v>40022005</v>
       </c>
       <c r="B15" s="25">
         <v>40</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="25">
         <v>2</v>
       </c>
-      <c r="D15" s="31">
-        <v>2004</v>
-      </c>
-      <c r="F15" s="30">
+      <c r="D15" s="24">
+        <v>2005</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="24">
         <v>8</v>
       </c>
-      <c r="G15" s="30" t="s">
-        <v>87</v>
+      <c r="G15" s="24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <f t="shared" si="0"/>
-        <v>40022005</v>
+        <v>40022006</v>
       </c>
       <c r="B16" s="25">
         <v>40</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="25">
         <v>2</v>
       </c>
-      <c r="D16" s="31">
-        <v>2005</v>
-      </c>
-      <c r="F16" s="30">
+      <c r="D16" s="24">
+        <v>2006</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="24">
         <v>6</v>
       </c>
-      <c r="G16" s="30" t="s">
-        <v>91</v>
+      <c r="G16" s="24" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
-        <v>40033000</v>
+        <v>40033001</v>
       </c>
       <c r="B17" s="25">
         <v>40</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="25">
         <v>3</v>
       </c>
-      <c r="D17" s="31">
-        <v>3000</v>
-      </c>
-      <c r="F17" s="30">
+      <c r="D17" s="24">
+        <v>3001</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="24">
         <v>9</v>
       </c>
-      <c r="G17" s="30" t="s">
-        <v>92</v>
+      <c r="G17" s="24" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEEC237-8889-4320-B03A-CAE26290B798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F152503E-1319-4D3E-A47D-5E34A4BD6B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2211,8 +2211,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -2368,7 +2369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2475,6 +2476,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5137,7 +5144,7 @@
   <cols>
     <col min="1" max="1" width="20.625" style="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
@@ -5318,13 +5325,13 @@
       <c r="B5" s="25">
         <v>40</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="36">
         <v>1</v>
       </c>
       <c r="D5" s="24">
         <v>1001</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="24">
@@ -5372,13 +5379,13 @@
       <c r="B6" s="25">
         <v>40</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="36">
         <v>1</v>
       </c>
       <c r="D6" s="24">
         <v>1002</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="25" t="s">
         <v>95</v>
       </c>
       <c r="F6" s="24">
@@ -5426,13 +5433,13 @@
       <c r="B7" s="25">
         <v>40</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="36">
         <v>1</v>
       </c>
       <c r="D7" s="24">
         <v>1003</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="25" t="s">
         <v>96</v>
       </c>
       <c r="F7" s="24">
@@ -5450,13 +5457,13 @@
       <c r="B8" s="25">
         <v>40</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="36">
         <v>1</v>
       </c>
       <c r="D8" s="24">
         <v>1004</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="25" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="24">
@@ -5474,13 +5481,13 @@
       <c r="B9" s="25">
         <v>40</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="36">
         <v>1</v>
       </c>
       <c r="D9" s="24">
         <v>1005</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="25" t="s">
         <v>98</v>
       </c>
       <c r="F9" s="24">
@@ -5498,13 +5505,13 @@
       <c r="B10" s="25">
         <v>40</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="36">
         <v>1</v>
       </c>
       <c r="D10" s="24">
         <v>1006</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="25" t="s">
         <v>99</v>
       </c>
       <c r="F10" s="24">
@@ -5522,13 +5529,13 @@
       <c r="B11" s="25">
         <v>40</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="36">
         <v>2</v>
       </c>
       <c r="D11" s="24">
         <v>2001</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="25" t="s">
         <v>100</v>
       </c>
       <c r="F11" s="24">
@@ -5546,13 +5553,13 @@
       <c r="B12" s="25">
         <v>40</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="36">
         <v>2</v>
       </c>
       <c r="D12" s="24">
         <v>2002</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="25" t="s">
         <v>101</v>
       </c>
       <c r="F12" s="24">
@@ -5570,13 +5577,13 @@
       <c r="B13" s="25">
         <v>40</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="36">
         <v>2</v>
       </c>
       <c r="D13" s="24">
         <v>2003</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="25" t="s">
         <v>102</v>
       </c>
       <c r="F13" s="24">
@@ -5594,13 +5601,13 @@
       <c r="B14" s="25">
         <v>40</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="36">
         <v>2</v>
       </c>
       <c r="D14" s="24">
         <v>2004</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="25" t="s">
         <v>103</v>
       </c>
       <c r="F14" s="24">
@@ -5618,13 +5625,13 @@
       <c r="B15" s="25">
         <v>40</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="36">
         <v>2</v>
       </c>
       <c r="D15" s="24">
         <v>2005</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="F15" s="24">
@@ -5642,13 +5649,13 @@
       <c r="B16" s="25">
         <v>40</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="36">
         <v>2</v>
       </c>
       <c r="D16" s="24">
         <v>2006</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="25" t="s">
         <v>105</v>
       </c>
       <c r="F16" s="24">
@@ -5666,13 +5673,13 @@
       <c r="B17" s="25">
         <v>40</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="36">
         <v>3</v>
       </c>
       <c r="D17" s="24">
         <v>3001</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="25" t="s">
         <v>106</v>
       </c>
       <c r="F17" s="24">

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F152503E-1319-4D3E-A47D-5E34A4BD6B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942049E6-551E-4AE6-91DC-78833323AEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1787,7 +1787,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2123,26 +2123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SP 소모 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스피드 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>받피증</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>속성 게이지 저항 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Table_Element_Status</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2204,6 +2184,25 @@
   </si>
   <si>
     <t>상태 이상 표시명 키값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Status_Category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Table_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>Buff_Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2211,9 +2210,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="00"/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -2369,7 +2369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2482,6 +2482,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5149,11 +5155,12 @@
     <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5161,6 +5168,7 @@
       <c r="E1"/>
       <c r="F1"/>
       <c r="G1"/>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -5176,7 +5184,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>81</v>
@@ -5184,8 +5192,10 @@
       <c r="G2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="32"/>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
@@ -5235,10 +5245,12 @@
         <v>82</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="29"/>
+        <v>68</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="33"/>
       <c r="J3" s="29"/>
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
@@ -5270,7 +5282,7 @@
     </row>
     <row r="4" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>57</v>
@@ -5284,10 +5296,16 @@
       <c r="E4" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="26"/>
+      <c r="F4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="34"/>
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
       <c r="L4" s="26"/>
@@ -5332,7 +5350,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F5" s="24">
         <v>1</v>
@@ -5340,8 +5358,10 @@
       <c r="G5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="25"/>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+      <c r="I5" s="35"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
@@ -5386,7 +5406,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F6" s="24">
         <v>2</v>
@@ -5394,8 +5414,10 @@
       <c r="G6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="35"/>
-      <c r="I6" s="25"/>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+      <c r="I6" s="35"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
@@ -5440,13 +5462,16 @@
         <v>1003</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F7" s="24">
         <v>3</v>
       </c>
-      <c r="G7" s="24" t="s">
-        <v>87</v>
+      <c r="G7" s="24">
+        <v>30001024</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0.85</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
@@ -5464,13 +5489,16 @@
         <v>1004</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F8" s="24">
         <v>4</v>
       </c>
-      <c r="G8" s="24" t="s">
-        <v>88</v>
+      <c r="G8" s="24">
+        <v>30001005</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0.85</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
@@ -5488,13 +5516,16 @@
         <v>1005</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F9" s="24">
         <v>5</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>86</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
@@ -5512,13 +5543,16 @@
         <v>1006</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F10" s="24">
         <v>6</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>86</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
@@ -5536,13 +5570,16 @@
         <v>2001</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="24" t="s">
-        <v>89</v>
+      <c r="G11" s="24">
+        <v>30001023</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
@@ -5560,13 +5597,16 @@
         <v>2002</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F12" s="24">
         <v>7</v>
       </c>
       <c r="G12" s="24" t="s">
         <v>86</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
@@ -5584,14 +5624,15 @@
         <v>2003</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F13" s="24">
         <v>3</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>87</v>
-      </c>
+      <c r="G13" s="24">
+        <v>30001024</v>
+      </c>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
@@ -5608,13 +5649,16 @@
         <v>2004</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F14" s="24">
         <v>4</v>
       </c>
-      <c r="G14" s="24" t="s">
-        <v>88</v>
+      <c r="G14" s="24">
+        <v>30001005</v>
+      </c>
+      <c r="H14" s="39">
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
@@ -5632,13 +5676,16 @@
         <v>2005</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F15" s="24">
         <v>8</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>86</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
@@ -5656,16 +5703,19 @@
         <v>2006</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F16" s="24">
         <v>6</v>
       </c>
-      <c r="G16" s="24" t="s">
-        <v>90</v>
+      <c r="G16" s="24">
+        <v>30001003</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
         <v>40033001</v>
@@ -5680,13 +5730,16 @@
         <v>3001</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F17" s="24">
         <v>9</v>
       </c>
-      <c r="G17" s="24" t="s">
-        <v>91</v>
+      <c r="G17" s="24">
+        <v>30001015</v>
+      </c>
+      <c r="H17" s="39">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942049E6-551E-4AE6-91DC-78833323AEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC7B3E8-634B-4D96-8A48-2E172741139F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2213,7 +2213,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="00"/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -2484,10 +2484,10 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5471,7 +5471,7 @@
         <v>30001024</v>
       </c>
       <c r="H7" s="39">
-        <v>0.85</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
@@ -5632,7 +5632,9 @@
       <c r="G13" s="24">
         <v>30001024</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="39">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="25">

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC7B3E8-634B-4D96-8A48-2E172741139F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0657255F-D544-4327-B766-C564E1126DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2104,13 +2104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:Element_Status_Category:NONE</t>
-  </si>
-  <si>
-    <t>enum:Element_Status_Category:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>버프 테이블 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2163,10 +2156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ELEMENT_STATUS_NAME_RADIAITON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ELEMENT_STATUS_NAME_BIND</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2203,6 +2192,17 @@
   </si>
   <si>
     <t>Buff_Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEMENT_STATUS_NAME_EXPOSURE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:ELEMENT_STATUS_CATEGORY:NONE</t>
+  </si>
+  <si>
+    <t>enum:ELEMENT_STATUS_CATEGORY:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -5153,14 +5153,14 @@
     <col min="3" max="3" width="13.875" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.25" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.875" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5184,16 +5184,16 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I2" s="32"/>
       <c r="J2" s="22"/>
@@ -5242,13 +5242,13 @@
         <v>36</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G3" s="29" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="29"/>
@@ -5282,7 +5282,7 @@
     </row>
     <row r="4" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>57</v>
@@ -5294,16 +5294,16 @@
         <v>61</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G4" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>107</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="26"/>
@@ -5350,13 +5350,13 @@
         <v>1001</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" s="24">
         <v>1</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H5" s="39">
         <v>0</v>
@@ -5406,13 +5406,13 @@
         <v>1002</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F6" s="24">
         <v>2</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H6" s="39">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>1003</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" s="24">
         <v>3</v>
@@ -5489,7 +5489,7 @@
         <v>1004</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F8" s="24">
         <v>4</v>
@@ -5516,13 +5516,13 @@
         <v>1005</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F9" s="24">
         <v>5</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H9" s="39">
         <v>0</v>
@@ -5543,13 +5543,13 @@
         <v>1006</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F10" s="24">
         <v>6</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H10" s="39">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>2001</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F11" s="24">
         <v>1</v>
@@ -5597,13 +5597,13 @@
         <v>2002</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F12" s="24">
         <v>7</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H12" s="39">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>2003</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F13" s="24">
         <v>3</v>
@@ -5651,7 +5651,7 @@
         <v>2004</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F14" s="24">
         <v>4</v>
@@ -5678,13 +5678,13 @@
         <v>2005</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F15" s="24">
         <v>8</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H15" s="39">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2006</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F16" s="24">
         <v>6</v>
@@ -5732,7 +5732,7 @@
         <v>3001</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F17" s="24">
         <v>9</v>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0657255F-D544-4327-B766-C564E1126DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79313D5-0D0A-4CD8-B090-5CB17B5AE7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1787,7 +1787,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="110">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2203,6 +2203,14 @@
   </si>
   <si>
     <t>enum:ELEMENT_STATUS_CATEGORY:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태 이상 지속턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Status_Duration_Turn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2327,7 +2335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2350,26 +2358,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2466,18 +2461,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2488,6 +2471,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5150,12 +5136,13 @@
   <cols>
     <col min="1" max="1" width="20.625" style="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.25" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.875" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
@@ -5169,6 +5156,7 @@
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
+      <c r="I1"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -5195,7 +5183,9 @@
       <c r="H2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="32"/>
+      <c r="I2" s="22" t="s">
+        <v>108</v>
+      </c>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
@@ -5250,7 +5240,9 @@
       <c r="H3" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="33"/>
+      <c r="I3" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="J3" s="29"/>
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
@@ -5305,7 +5297,9 @@
       <c r="H4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="34"/>
+      <c r="I4" s="26" t="s">
+        <v>109</v>
+      </c>
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
       <c r="L4" s="26"/>
@@ -5343,7 +5337,7 @@
       <c r="B5" s="25">
         <v>40</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="32">
         <v>1</v>
       </c>
       <c r="D5" s="24">
@@ -5358,10 +5352,12 @@
       <c r="G5" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="35">
         <v>0</v>
       </c>
-      <c r="I5" s="35"/>
+      <c r="I5" s="24">
+        <v>1</v>
+      </c>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
@@ -5399,7 +5395,7 @@
       <c r="B6" s="25">
         <v>40</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="32">
         <v>1</v>
       </c>
       <c r="D6" s="24">
@@ -5414,10 +5410,12 @@
       <c r="G6" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="35">
         <v>0</v>
       </c>
-      <c r="I6" s="35"/>
+      <c r="I6" s="24">
+        <v>0</v>
+      </c>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
@@ -5455,7 +5453,7 @@
       <c r="B7" s="25">
         <v>40</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="32">
         <v>1</v>
       </c>
       <c r="D7" s="24">
@@ -5470,8 +5468,11 @@
       <c r="G7" s="24">
         <v>30001024</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="35">
         <v>1.3</v>
+      </c>
+      <c r="I7" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
@@ -5482,7 +5483,7 @@
       <c r="B8" s="25">
         <v>40</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="32">
         <v>1</v>
       </c>
       <c r="D8" s="24">
@@ -5497,8 +5498,11 @@
       <c r="G8" s="24">
         <v>30001005</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="35">
         <v>0.85</v>
+      </c>
+      <c r="I8" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
@@ -5509,7 +5513,7 @@
       <c r="B9" s="25">
         <v>40</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="32">
         <v>1</v>
       </c>
       <c r="D9" s="24">
@@ -5524,8 +5528,11 @@
       <c r="G9" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="35">
         <v>0</v>
+      </c>
+      <c r="I9" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
@@ -5536,7 +5543,7 @@
       <c r="B10" s="25">
         <v>40</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="32">
         <v>1</v>
       </c>
       <c r="D10" s="24">
@@ -5551,8 +5558,11 @@
       <c r="G10" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="39">
+      <c r="H10" s="35">
         <v>0</v>
+      </c>
+      <c r="I10" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
@@ -5563,7 +5573,7 @@
       <c r="B11" s="25">
         <v>40</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="32">
         <v>2</v>
       </c>
       <c r="D11" s="24">
@@ -5578,8 +5588,11 @@
       <c r="G11" s="24">
         <v>30001023</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="35">
         <v>0.8</v>
+      </c>
+      <c r="I11" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
@@ -5590,7 +5603,7 @@
       <c r="B12" s="25">
         <v>40</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="32">
         <v>2</v>
       </c>
       <c r="D12" s="24">
@@ -5605,7 +5618,10 @@
       <c r="G12" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="35">
+        <v>0</v>
+      </c>
+      <c r="I12" s="36">
         <v>0</v>
       </c>
     </row>
@@ -5617,7 +5633,7 @@
       <c r="B13" s="25">
         <v>40</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="32">
         <v>2</v>
       </c>
       <c r="D13" s="24">
@@ -5632,8 +5648,11 @@
       <c r="G13" s="24">
         <v>30001024</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="35">
         <v>1.3</v>
+      </c>
+      <c r="I13" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
@@ -5644,7 +5663,7 @@
       <c r="B14" s="25">
         <v>40</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="32">
         <v>2</v>
       </c>
       <c r="D14" s="24">
@@ -5659,8 +5678,11 @@
       <c r="G14" s="24">
         <v>30001005</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="35">
         <v>0.7</v>
+      </c>
+      <c r="I14" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
@@ -5671,7 +5693,7 @@
       <c r="B15" s="25">
         <v>40</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="32">
         <v>2</v>
       </c>
       <c r="D15" s="24">
@@ -5686,8 +5708,11 @@
       <c r="G15" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="35">
         <v>0</v>
+      </c>
+      <c r="I15" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
@@ -5698,7 +5723,7 @@
       <c r="B16" s="25">
         <v>40</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="32">
         <v>2</v>
       </c>
       <c r="D16" s="24">
@@ -5713,11 +5738,14 @@
       <c r="G16" s="24">
         <v>30001003</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="35">
         <v>0.7</v>
       </c>
+      <c r="I16" s="36">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
         <v>40033001</v>
@@ -5725,7 +5753,7 @@
       <c r="B17" s="25">
         <v>40</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="32">
         <v>3</v>
       </c>
       <c r="D17" s="24">
@@ -5740,8 +5768,11 @@
       <c r="G17" s="24">
         <v>30001015</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="35">
         <v>0.7</v>
+      </c>
+      <c r="I17" s="36">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79313D5-0D0A-4CD8-B090-5CB17B5AE7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66B92E-948A-48D9-99C1-4942D8E9D62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -345,6 +345,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>제동우</author>
+    <author>전세혁</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F39414A5-AD79-44F4-8E5B-6901F30712C2}">
@@ -533,8 +534,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{126D906A-781A-4BA9-8A8E-7F63B254B92C}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{B0B74666-F72C-41F1-BE61-ADD7D16A76DF}">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>디버프가</t>
+        </r>
         <r>
           <rPr>
             <b/>
@@ -543,20 +555,18 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">0: NONE
-1: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">기절
-</t>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필요한</t>
         </r>
         <r>
           <rPr>
@@ -566,18 +576,18 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">2: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>매턴</t>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
         </r>
         <r>
           <rPr>
@@ -598,8 +608,8 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t xml:space="preserve">데미지
-</t>
+          <t>기입
+필요</t>
         </r>
         <r>
           <rPr>
@@ -609,18 +619,18 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">3: SP </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>소모량</t>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>없는</t>
         </r>
         <r>
           <rPr>
@@ -641,8 +651,7 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t xml:space="preserve">증가
-</t>
+          <t>경우</t>
         </r>
         <r>
           <rPr>
@@ -652,426 +661,22 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">4: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>스피드</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">감소
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">5: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>타겟</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>랜덤</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">지정
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">6: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>스킬</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">잠금
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">7: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>매턴</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>데미지</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>+</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>데미지</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">증가
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">8: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>공격</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>행동</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>아군</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>대상</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">지정
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">9: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>속성</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>게이지</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>저항</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>감소</t>
+          <t xml:space="preserve"> "-" </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입</t>
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{B0B74666-F72C-41F1-BE61-ADD7D16A76DF}">
+    <comment ref="G2" authorId="1" shapeId="0" xr:uid="{4402209D-9B48-4D1A-8A32-479F7E1CB0A0}">
       <text>
         <r>
           <rPr>
@@ -1082,134 +687,8 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>디버프가</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>필요한</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>경우</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>기입
-필요</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>없는</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>경우</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> "-" </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>기입</t>
+          <t>버프를 불러오는 경우,
+버프에 필요한 수치를 먼저 작성</t>
         </r>
       </text>
     </comment>
@@ -1787,7 +1266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="107">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2100,10 +1579,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상태 이상 카테고리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>버프 테이블 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2176,33 +1651,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Element_Status_Category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Buff_Table_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>버프 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>Buff_Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ELEMENT_STATUS_NAME_EXPOSURE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>enum:ELEMENT_STATUS_CATEGORY:NONE</t>
-  </si>
-  <si>
-    <t>enum:ELEMENT_STATUS_CATEGORY:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2211,6 +1668,17 @@
   </si>
   <si>
     <t>Element_Status_Duration_Turn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double[]</t>
+  </si>
+  <si>
+    <t>상태 이상 수치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Status_Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2364,7 +1832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2471,9 +1939,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4771,7 +4236,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -5131,7 +4596,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.625" style="31" bestFit="1" customWidth="1"/>
@@ -5139,15 +4604,14 @@
     <col min="3" max="3" width="13.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.25" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.875" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5156,9 +4620,8 @@
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
-      <c r="I1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>75</v>
       </c>
@@ -5172,20 +4635,18 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>108</v>
-      </c>
+      <c r="I2" s="22"/>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
@@ -5213,9 +4674,8 @@
       <c r="AH2" s="22"/>
       <c r="AI2" s="22"/>
       <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
     </row>
-    <row r="3" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>68</v>
       </c>
@@ -5232,17 +4692,15 @@
         <v>36</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="29" t="s">
         <v>56</v>
       </c>
+      <c r="I3" s="29"/>
       <c r="J3" s="29"/>
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
@@ -5270,11 +4728,10 @@
       <c r="AH3" s="29"/>
       <c r="AI3" s="29"/>
       <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
     </row>
-    <row r="4" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>57</v>
@@ -5286,20 +4743,18 @@
         <v>61</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>109</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I4" s="26"/>
       <c r="J4" s="26"/>
       <c r="K4" s="26"/>
       <c r="L4" s="26"/>
@@ -5327,9 +4782,8 @@
       <c r="AH4" s="26"/>
       <c r="AI4" s="26"/>
       <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>40011001</v>
@@ -5344,20 +4798,18 @@
         <v>1001</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="24">
+        <v>86</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="35">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
         <v>1</v>
       </c>
-      <c r="G5" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="35">
-        <v>0</v>
-      </c>
-      <c r="I5" s="24">
-        <v>1</v>
-      </c>
+      <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
@@ -5385,9 +4837,8 @@
       <c r="AH5" s="25"/>
       <c r="AI5" s="25"/>
       <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <f>(B6*1000000) + (C6*10000) + D6</f>
         <v>40011002</v>
@@ -5402,20 +4853,18 @@
         <v>1002</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="24">
-        <v>2</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="35">
+        <v>87</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="H6" s="24">
         <v>0</v>
       </c>
-      <c r="I6" s="24">
-        <v>0</v>
-      </c>
+      <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
@@ -5443,9 +4892,8 @@
       <c r="AH6" s="25"/>
       <c r="AI6" s="25"/>
       <c r="AJ6" s="25"/>
-      <c r="AK6" s="25"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <f t="shared" ref="A7:A17" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>40011003</v>
@@ -5460,22 +4908,19 @@
         <v>1003</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="24">
-        <v>3</v>
-      </c>
-      <c r="G7" s="24">
         <v>30001024</v>
       </c>
-      <c r="H7" s="35">
+      <c r="G7" s="35">
         <v>1.3</v>
       </c>
-      <c r="I7" s="36">
+      <c r="H7" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>40011004</v>
@@ -5490,22 +4935,19 @@
         <v>1004</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F8" s="24">
-        <v>4</v>
-      </c>
-      <c r="G8" s="24">
         <v>30001005</v>
       </c>
-      <c r="H8" s="35">
+      <c r="G8" s="35">
         <v>0.85</v>
       </c>
-      <c r="I8" s="36">
+      <c r="H8" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>40011005</v>
@@ -5520,22 +4962,19 @@
         <v>1005</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="24">
-        <v>5</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
-      </c>
-      <c r="I9" s="36">
+        <v>90</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="H9" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>40011006</v>
@@ -5550,22 +4989,19 @@
         <v>1006</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="24">
-        <v>6</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="35">
+        <v>91</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="35">
         <v>0</v>
       </c>
-      <c r="I10" s="36">
+      <c r="H10" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>40022001</v>
@@ -5580,22 +5016,19 @@
         <v>2001</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" s="24">
+        <v>30001023</v>
+      </c>
+      <c r="G11" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="H11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="24">
-        <v>30001023</v>
-      </c>
-      <c r="H11" s="35">
-        <v>0.8</v>
-      </c>
-      <c r="I11" s="36">
-        <v>1</v>
-      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <f t="shared" si="0"/>
         <v>40022002</v>
@@ -5610,22 +5043,19 @@
         <v>2002</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="24">
-        <v>7</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="35">
+        <v>93</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="24">
         <v>0</v>
       </c>
-      <c r="I12" s="36">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <f t="shared" si="0"/>
         <v>40022003</v>
@@ -5640,22 +5070,19 @@
         <v>2003</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="24">
-        <v>3</v>
-      </c>
-      <c r="G13" s="24">
-        <v>30001024</v>
-      </c>
-      <c r="H13" s="35">
-        <v>1.3</v>
-      </c>
-      <c r="I13" s="36">
+        <v>100</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <f t="shared" si="0"/>
         <v>40022004</v>
@@ -5670,22 +5097,19 @@
         <v>2004</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="24">
-        <v>4</v>
-      </c>
-      <c r="G14" s="24">
-        <v>30001005</v>
-      </c>
-      <c r="H14" s="35">
-        <v>0.7</v>
-      </c>
-      <c r="I14" s="36">
+        <v>94</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <f t="shared" si="0"/>
         <v>40022005</v>
@@ -5700,22 +5124,19 @@
         <v>2005</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F15" s="24">
-        <v>8</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="35">
-        <v>0</v>
-      </c>
-      <c r="I15" s="36">
+        <v>30001003</v>
+      </c>
+      <c r="G15" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <f t="shared" si="0"/>
         <v>40022006</v>
@@ -5730,22 +5151,19 @@
         <v>2006</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="24">
-        <v>6</v>
-      </c>
-      <c r="G16" s="24">
         <v>30001003</v>
       </c>
-      <c r="H16" s="35">
+      <c r="G16" s="35">
         <v>0.7</v>
       </c>
-      <c r="I16" s="36">
+      <c r="H16" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <f t="shared" si="0"/>
         <v>40033001</v>
@@ -5760,35 +5178,27 @@
         <v>3001</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="24">
-        <v>9</v>
-      </c>
-      <c r="G17" s="24">
         <v>30001015</v>
       </c>
-      <c r="H17" s="35">
+      <c r="G17" s="35">
         <v>0.7</v>
       </c>
-      <c r="I17" s="36">
+      <c r="H17" s="24">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1048576" xr:uid="{5F3CB115-75D3-4E18-94B1-D5ED884AD77E}">
-      <formula1>"0,1,2,3,4,5,6,7,8,9"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>

--- a/Assets/Data/DataTable/04_Element_Status.xlsx
+++ b/Assets/Data/DataTable/04_Element_Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66B92E-948A-48D9-99C1-4942D8E9D62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13733003-1F83-4C3F-9917-F806DD3ABF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -534,7 +534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{B0B74666-F72C-41F1-BE61-ADD7D16A76DF}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{B0B74666-F72C-41F1-BE61-ADD7D16A76DF}">
       <text>
         <r>
           <rPr>
@@ -676,7 +676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="1" shapeId="0" xr:uid="{4402209D-9B48-4D1A-8A32-479F7E1CB0A0}">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{4402209D-9B48-4D1A-8A32-479F7E1CB0A0}">
       <text>
         <r>
           <rPr>
@@ -719,7 +719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{C2095F88-B0F9-4F1B-B152-8ADD4BD51B2D}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{C2095F88-B0F9-4F1B-B152-8ADD4BD51B2D}">
       <text>
         <r>
           <rPr>
@@ -1266,7 +1266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4603,10 +4603,10 @@
     <col min="2" max="2" width="10.25" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.625" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -4635,16 +4635,16 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>98</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>102</v>
       </c>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
@@ -4689,16 +4689,16 @@
         <v>68</v>
       </c>
       <c r="E3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="29" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>56</v>
       </c>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -4743,16 +4743,16 @@
         <v>61</v>
       </c>
       <c r="E4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>82</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>103</v>
       </c>
       <c r="I4" s="26"/>
       <c r="J4" s="26"/>
@@ -4797,17 +4797,17 @@
       <c r="D5" s="24">
         <v>1001</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="35">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <v>1</v>
+      </c>
+      <c r="H5" s="25" t="s">
         <v>86</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="35">
-        <v>0</v>
-      </c>
-      <c r="H5" s="24">
-        <v>1</v>
       </c>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
@@ -4852,17 +4852,17 @@
       <c r="D6" s="24">
         <v>1002</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="24">
+        <v>30001025</v>
+      </c>
+      <c r="F6" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G6" s="35">
-        <v>0.3</v>
-      </c>
-      <c r="H6" s="24">
-        <v>0</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
@@ -4907,17 +4907,17 @@
       <c r="D7" s="24">
         <v>1003</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="24">
+        <v>30001024</v>
+      </c>
+      <c r="F7" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="F7" s="24">
-        <v>30001024</v>
-      </c>
-      <c r="G7" s="35">
-        <v>1.3</v>
-      </c>
-      <c r="H7" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
@@ -4934,17 +4934,17 @@
       <c r="D8" s="24">
         <v>1004</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="24">
+        <v>30001005</v>
+      </c>
+      <c r="F8" s="35">
+        <v>0.85</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0</v>
+      </c>
+      <c r="H8" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="F8" s="24">
-        <v>30001005</v>
-      </c>
-      <c r="G8" s="35">
-        <v>0.85</v>
-      </c>
-      <c r="H8" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
@@ -4961,17 +4961,17 @@
       <c r="D9" s="24">
         <v>1005</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="G9" s="24">
+        <v>1</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>90</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="35">
-        <v>0.7</v>
-      </c>
-      <c r="H9" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
@@ -4988,17 +4988,17 @@
       <c r="D10" s="24">
         <v>1006</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="35">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <v>1</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="35">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -5015,17 +5015,17 @@
       <c r="D11" s="24">
         <v>2001</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="24">
+        <v>30001023</v>
+      </c>
+      <c r="F11" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="G11" s="24">
+        <v>1</v>
+      </c>
+      <c r="H11" s="25" t="s">
         <v>92</v>
-      </c>
-      <c r="F11" s="24">
-        <v>30001023</v>
-      </c>
-      <c r="G11" s="35">
-        <v>1.3</v>
-      </c>
-      <c r="H11" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
@@ -5042,17 +5042,17 @@
       <c r="D12" s="24">
         <v>2002</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="24">
+        <v>30001025</v>
+      </c>
+      <c r="F12" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="24">
+        <v>0</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="H12" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
@@ -5069,17 +5069,17 @@
       <c r="D13" s="24">
         <v>2003</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0</v>
+      </c>
+      <c r="H13" s="25" t="s">
         <v>100</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
@@ -5096,17 +5096,17 @@
       <c r="D14" s="24">
         <v>2004</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="24">
+        <v>0</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>94</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="H14" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
@@ -5123,17 +5123,17 @@
       <c r="D15" s="24">
         <v>2005</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="24">
+        <v>30001003</v>
+      </c>
+      <c r="F15" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="G15" s="24">
+        <v>1</v>
+      </c>
+      <c r="H15" s="25" t="s">
         <v>95</v>
-      </c>
-      <c r="F15" s="24">
-        <v>30001003</v>
-      </c>
-      <c r="G15" s="35">
-        <v>1.3</v>
-      </c>
-      <c r="H15" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
@@ -5150,17 +5150,17 @@
       <c r="D16" s="24">
         <v>2006</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24">
+        <v>30001003</v>
+      </c>
+      <c r="F16" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="G16" s="24">
+        <v>1</v>
+      </c>
+      <c r="H16" s="25" t="s">
         <v>96</v>
-      </c>
-      <c r="F16" s="24">
-        <v>30001003</v>
-      </c>
-      <c r="G16" s="35">
-        <v>0.7</v>
-      </c>
-      <c r="H16" s="24">
-        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -5177,17 +5177,17 @@
       <c r="D17" s="24">
         <v>3001</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="24">
+        <v>30001015</v>
+      </c>
+      <c r="F17" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="G17" s="24">
+        <v>1</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="F17" s="24">
-        <v>30001015</v>
-      </c>
-      <c r="G17" s="35">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="24">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5203,7 +5203,7 @@
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:XFD3</xm:sqref>
+          <xm:sqref>A3:H3 J3:XFD3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
